--- a/summary_stats/chuuchuu_summary_2025_04.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_04.xlsx
@@ -1533,13 +1533,13 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1612,25 +1612,25 @@
         <v>89</v>
       </c>
       <c r="N15" t="n">
-        <v>855</v>
+        <v>823</v>
       </c>
       <c r="O15" t="n">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="P15" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="Q15" t="n">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="R15" t="n">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="S15" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="T15" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
         <v>1619</v>
@@ -1691,22 +1691,22 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
@@ -1849,25 +1849,25 @@
         <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O18" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P18" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q18" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>258</v>
@@ -1928,25 +1928,25 @@
         <v>509</v>
       </c>
       <c r="N19" t="n">
-        <v>2209</v>
+        <v>2018</v>
       </c>
       <c r="O19" t="n">
-        <v>1861</v>
+        <v>1678</v>
       </c>
       <c r="P19" t="n">
-        <v>1701</v>
+        <v>1522</v>
       </c>
       <c r="Q19" t="n">
-        <v>1275</v>
+        <v>1124</v>
       </c>
       <c r="R19" t="n">
-        <v>938</v>
+        <v>802</v>
       </c>
       <c r="S19" t="n">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="T19" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="U19" t="n">
         <v>3965</v>
@@ -2007,25 +2007,25 @@
         <v>138</v>
       </c>
       <c r="N20" t="n">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="O20" t="n">
-        <v>707</v>
+        <v>674</v>
       </c>
       <c r="P20" t="n">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="Q20" t="n">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="R20" t="n">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="S20" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="T20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="U20" t="n">
         <v>1730</v>
@@ -2165,25 +2165,25 @@
         <v>1645</v>
       </c>
       <c r="N22" t="n">
-        <v>7701</v>
+        <v>7218</v>
       </c>
       <c r="O22" t="n">
-        <v>6725</v>
+        <v>6274</v>
       </c>
       <c r="P22" t="n">
-        <v>6320</v>
+        <v>5889</v>
       </c>
       <c r="Q22" t="n">
-        <v>4977</v>
+        <v>4597</v>
       </c>
       <c r="R22" t="n">
-        <v>3862</v>
+        <v>3525</v>
       </c>
       <c r="S22" t="n">
-        <v>1940</v>
+        <v>1727</v>
       </c>
       <c r="T22" t="n">
-        <v>630</v>
+        <v>539</v>
       </c>
       <c r="U22" t="n">
         <v>12398</v>
@@ -2244,25 +2244,25 @@
         <v>331</v>
       </c>
       <c r="N23" t="n">
-        <v>1778</v>
+        <v>1629</v>
       </c>
       <c r="O23" t="n">
-        <v>1497</v>
+        <v>1355</v>
       </c>
       <c r="P23" t="n">
-        <v>1421</v>
+        <v>1283</v>
       </c>
       <c r="Q23" t="n">
-        <v>1059</v>
+        <v>937</v>
       </c>
       <c r="R23" t="n">
-        <v>826</v>
+        <v>717</v>
       </c>
       <c r="S23" t="n">
-        <v>447</v>
+        <v>372</v>
       </c>
       <c r="T23" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="U23" t="n">
         <v>2821</v>
@@ -2560,25 +2560,25 @@
         <v>28</v>
       </c>
       <c r="N27" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="O27" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="P27" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Q27" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="R27" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="S27" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="T27" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="U27" t="n">
         <v>462</v>
@@ -2797,25 +2797,25 @@
         <v>20</v>
       </c>
       <c r="N30" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O30" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="P30" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="Q30" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="R30" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
         <v>542</v>
@@ -2955,19 +2955,19 @@
         <v>15</v>
       </c>
       <c r="N32" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O32" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P32" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q32" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="R32" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="S32" t="n">
         <v>30</v>
@@ -3824,25 +3824,25 @@
         <v>372</v>
       </c>
       <c r="N43" t="n">
-        <v>884</v>
+        <v>792</v>
       </c>
       <c r="O43" t="n">
-        <v>874</v>
+        <v>782</v>
       </c>
       <c r="P43" t="n">
-        <v>860</v>
+        <v>771</v>
       </c>
       <c r="Q43" t="n">
-        <v>636</v>
+        <v>569</v>
       </c>
       <c r="R43" t="n">
-        <v>505</v>
+        <v>446</v>
       </c>
       <c r="S43" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="T43" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="U43" t="n">
         <v>3227</v>
@@ -3982,25 +3982,25 @@
         <v>33</v>
       </c>
       <c r="N45" t="n">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="O45" t="n">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="P45" t="n">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="Q45" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="R45" t="n">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S45" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="T45" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="U45" t="n">
         <v>461</v>
@@ -4061,22 +4061,22 @@
         <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="n">
         <v>4</v>
@@ -5167,19 +5167,19 @@
         <v>24</v>
       </c>
       <c r="N60" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P60" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q60" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -5246,22 +5246,22 @@
         <v>4978</v>
       </c>
       <c r="N61" t="n">
-        <v>2980</v>
+        <v>2896</v>
       </c>
       <c r="O61" t="n">
-        <v>1726</v>
+        <v>1669</v>
       </c>
       <c r="P61" t="n">
-        <v>1341</v>
+        <v>1294</v>
       </c>
       <c r="Q61" t="n">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="R61" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="S61" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -5325,25 +5325,25 @@
         <v>35</v>
       </c>
       <c r="N62" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O62" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="P62" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="Q62" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="R62" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="S62" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U62" t="n">
         <v>379</v>
@@ -5483,22 +5483,22 @@
         <v>668</v>
       </c>
       <c r="N64" t="n">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="O64" t="n">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="P64" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="Q64" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="R64" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -5562,25 +5562,25 @@
         <v>30</v>
       </c>
       <c r="N65" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="O65" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="P65" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="Q65" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="R65" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="S65" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
         <v>409</v>
@@ -5641,19 +5641,19 @@
         <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O66" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P66" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q66" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R66" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S66" t="n">
         <v>41</v>
@@ -5720,19 +5720,19 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5799,19 +5799,19 @@
         <v>348</v>
       </c>
       <c r="N68" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O68" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P68" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q68" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -5957,22 +5957,22 @@
         <v>8093</v>
       </c>
       <c r="N70" t="n">
-        <v>3984</v>
+        <v>3877</v>
       </c>
       <c r="O70" t="n">
-        <v>1879</v>
+        <v>1820</v>
       </c>
       <c r="P70" t="n">
-        <v>1394</v>
+        <v>1348</v>
       </c>
       <c r="Q70" t="n">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="R70" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="S70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
@@ -6036,25 +6036,25 @@
         <v>3743</v>
       </c>
       <c r="N71" t="n">
-        <v>1685</v>
+        <v>1639</v>
       </c>
       <c r="O71" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="P71" t="n">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="Q71" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="R71" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U71" t="n">
         <v>31343</v>
@@ -6194,16 +6194,16 @@
         <v>19</v>
       </c>
       <c r="N73" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O73" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P73" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q73" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R73" t="n">
         <v>17</v>
@@ -7300,25 +7300,25 @@
         <v>70</v>
       </c>
       <c r="N87" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="O87" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="P87" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Q87" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R87" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
         <v>1903</v>
@@ -7537,10 +7537,10 @@
         <v>21</v>
       </c>
       <c r="N90" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O90" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P90" t="n">
         <v>219</v>
@@ -8090,25 +8090,25 @@
         <v>7</v>
       </c>
       <c r="N97" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O97" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P97" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Q97" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R97" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S97" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T97" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U97" t="n">
         <v>1733</v>
@@ -8880,19 +8880,19 @@
         <v>61</v>
       </c>
       <c r="N107" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O107" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P107" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q107" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R107" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S107" t="n">
         <v>52</v>
@@ -9275,19 +9275,19 @@
         <v>77</v>
       </c>
       <c r="N112" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O112" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P112" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q112" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R112" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S112" t="n">
         <v>18</v>
@@ -9512,22 +9512,22 @@
         <v>169</v>
       </c>
       <c r="N115" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O115" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P115" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q115" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R115" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S115" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T115" t="n">
         <v>8</v>
@@ -9591,25 +9591,25 @@
         <v>175</v>
       </c>
       <c r="N116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
         <v>11928</v>
@@ -10144,19 +10144,19 @@
         <v>6</v>
       </c>
       <c r="N123" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O123" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P123" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q123" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R123" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S123" t="n">
         <v>23</v>
@@ -10539,22 +10539,22 @@
         <v>65</v>
       </c>
       <c r="N128" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="O128" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P128" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="Q128" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="R128" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S128" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T128" t="n">
         <v>0</v>
@@ -10697,25 +10697,25 @@
         <v>548</v>
       </c>
       <c r="N130" t="n">
-        <v>4548</v>
+        <v>4464</v>
       </c>
       <c r="O130" t="n">
-        <v>2754</v>
+        <v>2684</v>
       </c>
       <c r="P130" t="n">
-        <v>2238</v>
+        <v>2179</v>
       </c>
       <c r="Q130" t="n">
-        <v>1123</v>
+        <v>1084</v>
       </c>
       <c r="R130" t="n">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="S130" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="T130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U130" t="n">
         <v>24008</v>
@@ -10776,22 +10776,22 @@
         <v>32</v>
       </c>
       <c r="N131" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O131" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P131" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q131" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R131" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T131" t="n">
         <v>0</v>
@@ -11013,22 +11013,22 @@
         <v>19</v>
       </c>
       <c r="N134" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O134" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P134" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Q134" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R134" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S134" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T134" t="n">
         <v>2</v>
@@ -11092,22 +11092,22 @@
         <v>113</v>
       </c>
       <c r="N135" t="n">
-        <v>2122</v>
+        <v>2112</v>
       </c>
       <c r="O135" t="n">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="P135" t="n">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="Q135" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="R135" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="S135" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T135" t="n">
         <v>0</v>
@@ -11171,19 +11171,19 @@
         <v>22</v>
       </c>
       <c r="N136" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O136" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P136" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q136" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R136" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -11408,22 +11408,22 @@
         <v>51</v>
       </c>
       <c r="N139" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="O139" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P139" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q139" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R139" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S139" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T139" t="n">
         <v>0</v>
@@ -11566,22 +11566,22 @@
         <v>254</v>
       </c>
       <c r="N141" t="n">
-        <v>2997</v>
+        <v>2968</v>
       </c>
       <c r="O141" t="n">
-        <v>1628</v>
+        <v>1607</v>
       </c>
       <c r="P141" t="n">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="Q141" t="n">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="R141" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="S141" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T141" t="n">
         <v>4</v>
@@ -11645,16 +11645,16 @@
         <v>89</v>
       </c>
       <c r="N142" t="n">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="O142" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="P142" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="Q142" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R142" t="n">
         <v>55</v>
@@ -11882,16 +11882,16 @@
         <v>7</v>
       </c>
       <c r="N145" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O145" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P145" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q145" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R145" t="n">
         <v>9</v>
@@ -12040,25 +12040,25 @@
         <v>8</v>
       </c>
       <c r="N147" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O147" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P147" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q147" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R147" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="S147" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U147" t="n">
         <v>650</v>
@@ -12198,25 +12198,25 @@
         <v>28</v>
       </c>
       <c r="N149" t="n">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="O149" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="P149" t="n">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="Q149" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R149" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S149" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T149" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U149" t="n">
         <v>2003</v>
@@ -12356,25 +12356,25 @@
         <v>2</v>
       </c>
       <c r="N151" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O151" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P151" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q151" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R151" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S151" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U151" t="n">
         <v>140</v>
@@ -12593,25 +12593,25 @@
         <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O154" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P154" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q154" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R154" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S154" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U154" t="n">
         <v>1027</v>
@@ -12988,25 +12988,25 @@
         <v>110</v>
       </c>
       <c r="N159" t="n">
-        <v>3154</v>
+        <v>3119</v>
       </c>
       <c r="O159" t="n">
-        <v>1723</v>
+        <v>1696</v>
       </c>
       <c r="P159" t="n">
-        <v>1723</v>
+        <v>1696</v>
       </c>
       <c r="Q159" t="n">
-        <v>1092</v>
+        <v>1068</v>
       </c>
       <c r="R159" t="n">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="S159" t="n">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="T159" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="U159" t="n">
         <v>13941</v>
@@ -13067,25 +13067,25 @@
         <v>22</v>
       </c>
       <c r="N160" t="n">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O160" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="P160" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="Q160" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R160" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="S160" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T160" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U160" t="n">
         <v>963</v>
@@ -13778,19 +13778,19 @@
         <v>11</v>
       </c>
       <c r="N169" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="O169" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P169" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q169" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R169" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S169" t="n">
         <v>46</v>
@@ -14252,25 +14252,25 @@
         <v>2</v>
       </c>
       <c r="N175" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O175" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P175" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q175" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R175" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S175" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T175" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U175" t="n">
         <v>283</v>
@@ -14331,25 +14331,25 @@
         <v>12</v>
       </c>
       <c r="N176" t="n">
-        <v>2719</v>
+        <v>2714</v>
       </c>
       <c r="O176" t="n">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="P176" t="n">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="Q176" t="n">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="R176" t="n">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="S176" t="n">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="T176" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="U176" t="n">
         <v>6588</v>
@@ -14410,25 +14410,25 @@
         <v>16</v>
       </c>
       <c r="N177" t="n">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="O177" t="n">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="P177" t="n">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="Q177" t="n">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="R177" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="S177" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="T177" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U177" t="n">
         <v>2809</v>
@@ -14805,16 +14805,16 @@
         <v>110</v>
       </c>
       <c r="N182" t="n">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="O182" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P182" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q182" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R182" t="n">
         <v>36</v>
@@ -15121,22 +15121,22 @@
         <v>6</v>
       </c>
       <c r="N186" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O186" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P186" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q186" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R186" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S186" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T186" t="n">
         <v>3</v>
@@ -15200,25 +15200,25 @@
         <v>4050</v>
       </c>
       <c r="N187" t="n">
-        <v>39741</v>
+        <v>39380</v>
       </c>
       <c r="O187" t="n">
-        <v>21597</v>
+        <v>21346</v>
       </c>
       <c r="P187" t="n">
-        <v>16877</v>
+        <v>16664</v>
       </c>
       <c r="Q187" t="n">
-        <v>8459</v>
+        <v>8315</v>
       </c>
       <c r="R187" t="n">
-        <v>4817</v>
+        <v>4710</v>
       </c>
       <c r="S187" t="n">
-        <v>1523</v>
+        <v>1483</v>
       </c>
       <c r="T187" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="U187" t="n">
         <v>213216</v>
@@ -15279,22 +15279,22 @@
         <v>115</v>
       </c>
       <c r="N188" t="n">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="O188" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P188" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q188" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R188" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S188" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T188" t="n">
         <v>1</v>
@@ -17084,25 +17084,25 @@
         <v>5</v>
       </c>
       <c r="N211" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="O211" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P211" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="Q211" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R211" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S211" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T211" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U211" t="n">
         <v>324</v>
@@ -17610,25 +17610,25 @@
         <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V2" t="n">
         <v>575</v>
@@ -18030,25 +18030,25 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>1027</v>
@@ -18198,16 +18198,16 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -18534,25 +18534,25 @@
         <v>28</v>
       </c>
       <c r="O13" t="n">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="P13" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="Q13" t="n">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="R13" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="S13" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="T13" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V13" t="n">
         <v>2003</v>
@@ -18702,25 +18702,25 @@
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
         <v>140</v>
@@ -18954,25 +18954,25 @@
         <v>110</v>
       </c>
       <c r="O18" t="n">
-        <v>3154</v>
+        <v>3119</v>
       </c>
       <c r="P18" t="n">
-        <v>1723</v>
+        <v>1696</v>
       </c>
       <c r="Q18" t="n">
-        <v>1723</v>
+        <v>1696</v>
       </c>
       <c r="R18" t="n">
-        <v>1092</v>
+        <v>1068</v>
       </c>
       <c r="S18" t="n">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="T18" t="n">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="U18" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="V18" t="n">
         <v>13941</v>
@@ -19038,25 +19038,25 @@
         <v>22</v>
       </c>
       <c r="O19" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="P19" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="Q19" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="R19" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="S19" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="T19" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V19" t="n">
         <v>930</v>
@@ -19332,25 +19332,25 @@
         <v>19</v>
       </c>
       <c r="O2" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="P2" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Q2" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R2" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S2" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
         <v>291</v>
@@ -19584,22 +19584,22 @@
         <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -19668,25 +19668,25 @@
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>53</v>
@@ -19752,19 +19752,19 @@
         <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
         <v>5</v>
@@ -19920,22 +19920,22 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -20004,25 +20004,25 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
         <v>27</v>
@@ -20088,25 +20088,25 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>22</v>
@@ -20172,13 +20172,13 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -20424,25 +20424,25 @@
         <v>509</v>
       </c>
       <c r="O15" t="n">
-        <v>2196</v>
+        <v>2005</v>
       </c>
       <c r="P15" t="n">
-        <v>1852</v>
+        <v>1669</v>
       </c>
       <c r="Q15" t="n">
-        <v>1695</v>
+        <v>1516</v>
       </c>
       <c r="R15" t="n">
-        <v>1269</v>
+        <v>1118</v>
       </c>
       <c r="S15" t="n">
-        <v>936</v>
+        <v>800</v>
       </c>
       <c r="T15" t="n">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="U15" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
         <v>3947</v>
@@ -20508,25 +20508,25 @@
         <v>39</v>
       </c>
       <c r="O16" t="n">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="P16" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q16" t="n">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="R16" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="S16" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="T16" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="U16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="V16" t="n">
         <v>436</v>
@@ -20676,25 +20676,25 @@
         <v>1644</v>
       </c>
       <c r="O18" t="n">
-        <v>7696</v>
+        <v>7213</v>
       </c>
       <c r="P18" t="n">
-        <v>6721</v>
+        <v>6270</v>
       </c>
       <c r="Q18" t="n">
-        <v>6316</v>
+        <v>5885</v>
       </c>
       <c r="R18" t="n">
-        <v>4975</v>
+        <v>4595</v>
       </c>
       <c r="S18" t="n">
-        <v>3860</v>
+        <v>3523</v>
       </c>
       <c r="T18" t="n">
-        <v>1940</v>
+        <v>1727</v>
       </c>
       <c r="U18" t="n">
-        <v>630</v>
+        <v>539</v>
       </c>
       <c r="V18" t="n">
         <v>12392</v>
@@ -21516,25 +21516,25 @@
         <v>51</v>
       </c>
       <c r="O28" t="n">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="P28" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="Q28" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="R28" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="S28" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="T28" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V28" t="n">
         <v>393</v>
@@ -21600,25 +21600,25 @@
         <v>24</v>
       </c>
       <c r="O29" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P29" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="Q29" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="R29" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S29" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="T29" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
         <v>181</v>
@@ -21684,22 +21684,22 @@
         <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="P30" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R30" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T30" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U30" t="n">
         <v>4</v>
@@ -21768,25 +21768,25 @@
         <v>99</v>
       </c>
       <c r="O31" t="n">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="P31" t="n">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="Q31" t="n">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="R31" t="n">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="S31" t="n">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="T31" t="n">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="U31" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="V31" t="n">
         <v>606</v>
@@ -21852,22 +21852,22 @@
         <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P32" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Q32" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="R32" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32" t="n">
         <v>5</v>
@@ -22188,22 +22188,22 @@
         <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
@@ -22272,25 +22272,25 @@
         <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P37" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q37" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S37" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>198</v>
@@ -22440,25 +22440,25 @@
         <v>20</v>
       </c>
       <c r="O39" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="P39" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="Q39" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="R39" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="S39" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="T39" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U39" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V39" t="n">
         <v>75</v>
@@ -22692,25 +22692,25 @@
         <v>37</v>
       </c>
       <c r="O42" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="P42" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="Q42" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R42" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="S42" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="T42" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V42" t="n">
         <v>261</v>
@@ -22776,25 +22776,25 @@
         <v>135</v>
       </c>
       <c r="O43" t="n">
-        <v>556</v>
+        <v>483</v>
       </c>
       <c r="P43" t="n">
-        <v>496</v>
+        <v>426</v>
       </c>
       <c r="Q43" t="n">
-        <v>463</v>
+        <v>396</v>
       </c>
       <c r="R43" t="n">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="S43" t="n">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="T43" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="U43" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="V43" t="n">
         <v>835</v>
@@ -22860,22 +22860,22 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -22944,25 +22944,25 @@
         <v>27</v>
       </c>
       <c r="O45" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="P45" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="Q45" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="R45" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="S45" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="T45" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>408</v>
@@ -23028,22 +23028,22 @@
         <v>14</v>
       </c>
       <c r="O46" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P46" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q46" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="R46" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="S46" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="T46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U46" t="n">
         <v>4</v>
@@ -23532,25 +23532,25 @@
         <v>28</v>
       </c>
       <c r="O52" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="P52" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="Q52" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="R52" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="S52" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="T52" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="U52" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="V52" t="n">
         <v>462</v>
@@ -23784,19 +23784,19 @@
         <v>15</v>
       </c>
       <c r="O55" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="P55" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q55" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R55" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S55" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T55" t="n">
         <v>30</v>
@@ -24204,19 +24204,19 @@
         <v>43</v>
       </c>
       <c r="O60" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P60" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q60" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R60" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S60" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T60" t="n">
         <v>24</v>
@@ -24834,25 +24834,25 @@
         <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="P2" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Q2" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="R2" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="S2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="T2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
         <v>351</v>
@@ -25002,25 +25002,25 @@
         <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="P4" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="Q4" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="R4" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="S4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="T4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>409</v>
@@ -25254,22 +25254,22 @@
         <v>4978</v>
       </c>
       <c r="O7" t="n">
-        <v>2980</v>
+        <v>2896</v>
       </c>
       <c r="P7" t="n">
-        <v>1726</v>
+        <v>1669</v>
       </c>
       <c r="Q7" t="n">
-        <v>1341</v>
+        <v>1294</v>
       </c>
       <c r="R7" t="n">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="S7" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="T7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -25422,22 +25422,22 @@
         <v>668</v>
       </c>
       <c r="O9" t="n">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="P9" t="n">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="Q9" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="R9" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="S9" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="T9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
@@ -25506,19 +25506,19 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -25590,19 +25590,19 @@
         <v>348</v>
       </c>
       <c r="O11" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -25758,22 +25758,22 @@
         <v>8093</v>
       </c>
       <c r="O13" t="n">
-        <v>3984</v>
+        <v>3877</v>
       </c>
       <c r="P13" t="n">
-        <v>1879</v>
+        <v>1820</v>
       </c>
       <c r="Q13" t="n">
-        <v>1394</v>
+        <v>1348</v>
       </c>
       <c r="R13" t="n">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="S13" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="T13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -25842,25 +25842,25 @@
         <v>3743</v>
       </c>
       <c r="O14" t="n">
-        <v>1685</v>
+        <v>1639</v>
       </c>
       <c r="P14" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="Q14" t="n">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="R14" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="S14" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="T14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
         <v>31343</v>
@@ -26094,19 +26094,19 @@
         <v>24</v>
       </c>
       <c r="O17" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T17" t="n">
         <v>7</v>
@@ -26178,19 +26178,19 @@
         <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R18" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S18" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T18" t="n">
         <v>41</v>
@@ -29328,16 +29328,16 @@
         <v>19</v>
       </c>
       <c r="O37" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P37" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S37" t="n">
         <v>17</v>
@@ -30084,25 +30084,25 @@
         <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P46" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Q46" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="R46" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="S46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>1903</v>
@@ -30336,10 +30336,10 @@
         <v>21</v>
       </c>
       <c r="O49" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P49" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q49" t="n">
         <v>219</v>
@@ -31890,19 +31890,19 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
         <v>6</v>
@@ -32226,19 +32226,19 @@
         <v>27</v>
       </c>
       <c r="O12" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T12" t="n">
         <v>14</v>
@@ -32310,22 +32310,22 @@
         <v>169</v>
       </c>
       <c r="O13" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P13" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="R13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U13" t="n">
         <v>8</v>
@@ -32814,19 +32814,19 @@
         <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
         <v>23</v>
@@ -33738,25 +33738,25 @@
         <v>175</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>11928</v>
@@ -34620,22 +34620,22 @@
         <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="T3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -34704,22 +34704,22 @@
         <v>65</v>
       </c>
       <c r="O4" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="P4" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="Q4" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="R4" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="T4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -35040,25 +35040,25 @@
         <v>548</v>
       </c>
       <c r="O8" t="n">
-        <v>4548</v>
+        <v>4464</v>
       </c>
       <c r="P8" t="n">
-        <v>2754</v>
+        <v>2684</v>
       </c>
       <c r="Q8" t="n">
-        <v>2238</v>
+        <v>2179</v>
       </c>
       <c r="R8" t="n">
-        <v>1123</v>
+        <v>1084</v>
       </c>
       <c r="S8" t="n">
-        <v>622</v>
+        <v>593</v>
       </c>
       <c r="T8" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8" t="n">
         <v>24008</v>
@@ -35124,22 +35124,22 @@
         <v>32</v>
       </c>
       <c r="O9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P9" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -35292,22 +35292,22 @@
         <v>113</v>
       </c>
       <c r="O11" t="n">
-        <v>2122</v>
+        <v>2112</v>
       </c>
       <c r="P11" t="n">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="Q11" t="n">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="R11" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="S11" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="T11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -35376,19 +35376,19 @@
         <v>22</v>
       </c>
       <c r="O12" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T12" t="n">
         <v>4</v>
@@ -35544,22 +35544,22 @@
         <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="P14" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="Q14" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -35712,22 +35712,22 @@
         <v>254</v>
       </c>
       <c r="O16" t="n">
-        <v>2997</v>
+        <v>2968</v>
       </c>
       <c r="P16" t="n">
-        <v>1628</v>
+        <v>1607</v>
       </c>
       <c r="Q16" t="n">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="R16" t="n">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="S16" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="T16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U16" t="n">
         <v>4</v>
@@ -35796,16 +35796,16 @@
         <v>88</v>
       </c>
       <c r="O17" t="n">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="P17" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="Q17" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="R17" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="S17" t="n">
         <v>55</v>
@@ -36678,22 +36678,22 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
@@ -37602,19 +37602,19 @@
         <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P19" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q19" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R19" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T19" t="n">
         <v>23</v>
@@ -38190,25 +38190,25 @@
         <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P26" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q26" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R26" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="T26" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V26" t="n">
         <v>283</v>
@@ -38274,25 +38274,25 @@
         <v>12</v>
       </c>
       <c r="O27" t="n">
-        <v>2719</v>
+        <v>2714</v>
       </c>
       <c r="P27" t="n">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="Q27" t="n">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="R27" t="n">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="S27" t="n">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="T27" t="n">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="U27" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="V27" t="n">
         <v>6588</v>
@@ -38358,25 +38358,25 @@
         <v>16</v>
       </c>
       <c r="O28" t="n">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="P28" t="n">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="Q28" t="n">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="R28" t="n">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="S28" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="T28" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="U28" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="V28" t="n">
         <v>2809</v>
@@ -38610,16 +38610,16 @@
         <v>110</v>
       </c>
       <c r="O31" t="n">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="P31" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q31" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S31" t="n">
         <v>36</v>
@@ -38862,25 +38862,25 @@
         <v>4050</v>
       </c>
       <c r="O34" t="n">
-        <v>39741</v>
+        <v>39380</v>
       </c>
       <c r="P34" t="n">
-        <v>21597</v>
+        <v>21346</v>
       </c>
       <c r="Q34" t="n">
-        <v>16877</v>
+        <v>16664</v>
       </c>
       <c r="R34" t="n">
-        <v>8459</v>
+        <v>8315</v>
       </c>
       <c r="S34" t="n">
-        <v>4817</v>
+        <v>4710</v>
       </c>
       <c r="T34" t="n">
-        <v>1523</v>
+        <v>1483</v>
       </c>
       <c r="U34" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="V34" t="n">
         <v>213216</v>
@@ -38946,22 +38946,22 @@
         <v>115</v>
       </c>
       <c r="O35" t="n">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="P35" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="Q35" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R35" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S35" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U35" t="n">
         <v>1</v>

--- a/summary_stats/chuuchuu_summary_2025_04.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_04.xlsx
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -17026,7 +17026,7 @@
         <v>2</v>
       </c>
       <c r="U210" t="n">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="211">
@@ -17072,7 +17072,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -17084,16 +17084,16 @@
         <v>5</v>
       </c>
       <c r="N211" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O211" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P211" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q211" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R211" t="n">
         <v>30</v>
@@ -17105,7 +17105,7 @@
         <v>3</v>
       </c>
       <c r="U211" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="212">
